--- a/research/traditional_assets/database/data/italy/italy_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0347</v>
+        <v>0.003395</v>
       </c>
       <c r="E2">
-        <v>0.11545</v>
+        <v>0.0387</v>
       </c>
       <c r="F2">
-        <v>0.25</v>
+        <v>0.15575</v>
       </c>
       <c r="G2">
-        <v>0.07241466280955715</v>
+        <v>0.08642148712447482</v>
       </c>
       <c r="H2">
-        <v>0.07241449308225459</v>
+        <v>0.08642148712447482</v>
       </c>
       <c r="I2">
-        <v>0.0600132081019204</v>
+        <v>0.06673845134695175</v>
       </c>
       <c r="J2">
-        <v>0.04847890375890386</v>
+        <v>0.0483146850900994</v>
       </c>
       <c r="K2">
-        <v>4811.97</v>
+        <v>4129.6</v>
       </c>
       <c r="L2">
-        <v>0.0326689075196663</v>
+        <v>0.03625197298308019</v>
       </c>
       <c r="M2">
-        <v>2742.985</v>
+        <v>3554.81</v>
       </c>
       <c r="N2">
-        <v>0.06057829063604241</v>
+        <v>0.09334448450346221</v>
       </c>
       <c r="O2">
-        <v>0.570033686826809</v>
+        <v>0.860812185199535</v>
       </c>
       <c r="P2">
-        <v>2742.985</v>
+        <v>3519.83</v>
       </c>
       <c r="Q2">
-        <v>0.06057829063604241</v>
+        <v>0.0924259571931612</v>
       </c>
       <c r="R2">
-        <v>0.570033686826809</v>
+        <v>0.8523416311507167</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>34.97999999999996</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.00984018836449767</v>
       </c>
       <c r="U2">
-        <v>12766.4</v>
+        <v>10985.39</v>
       </c>
       <c r="V2">
-        <v>0.2819434628975265</v>
+        <v>0.2884614273672823</v>
       </c>
       <c r="W2">
-        <v>0.1320469798657718</v>
+        <v>0.07854782032369236</v>
       </c>
       <c r="X2">
-        <v>0.0761687074738237</v>
+        <v>0.1221121546536321</v>
       </c>
       <c r="Y2">
-        <v>0.05587827239194812</v>
+        <v>-0.04356433432993977</v>
       </c>
       <c r="Z2">
-        <v>2.698542154283064</v>
+        <v>1.931813153836593</v>
       </c>
       <c r="AA2">
-        <v>0.1275193538409877</v>
+        <v>0.09397349534423517</v>
       </c>
       <c r="AB2">
-        <v>0.06151351716485386</v>
+        <v>0.0994951487178409</v>
       </c>
       <c r="AC2">
-        <v>0.06450946368257</v>
+        <v>-0.005893744676148435</v>
       </c>
       <c r="AD2">
-        <v>30525</v>
+        <v>27682.6</v>
       </c>
       <c r="AE2">
-        <v>4.692556534121173</v>
+        <v>5.297004768038788</v>
       </c>
       <c r="AF2">
-        <v>30529.69255653412</v>
+        <v>27687.89700476804</v>
       </c>
       <c r="AG2">
-        <v>17763.29255653412</v>
+        <v>16702.50700476804</v>
       </c>
       <c r="AH2">
-        <v>0.4027148973565219</v>
+        <v>0.4209768234696245</v>
       </c>
       <c r="AI2">
-        <v>0.3468183966454388</v>
+        <v>0.4257934180799565</v>
       </c>
       <c r="AJ2">
-        <v>0.2817634015641692</v>
+        <v>0.3048725726876307</v>
       </c>
       <c r="AK2">
-        <v>0.2360209976328981</v>
+        <v>0.3090698363434848</v>
       </c>
       <c r="AL2">
-        <v>1231.22</v>
+        <v>1039.81</v>
       </c>
       <c r="AM2">
-        <v>1231.061</v>
+        <v>1039.81</v>
       </c>
       <c r="AN2">
-        <v>2.882956227232674</v>
+        <v>3.097911903570882</v>
       </c>
       <c r="AO2">
-        <v>7.176377901593541</v>
+        <v>7.306911839663016</v>
       </c>
       <c r="AP2">
-        <v>1.677667318329757</v>
+        <v>1.869148680743389</v>
       </c>
       <c r="AQ2">
-        <v>7.177304780185547</v>
+        <v>7.306911839663016</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Assiteca S.p.A. (BIT:ASSI)</t>
+          <t>Net Insurance S.p.A. (BIT:NET)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07339999999999999</v>
-      </c>
-      <c r="E3">
-        <v>0.15</v>
+        <v>0.181</v>
+      </c>
+      <c r="F3">
+        <v>0.239</v>
       </c>
       <c r="G3">
-        <v>0.1513157894736842</v>
+        <v>0.2341526520051747</v>
       </c>
       <c r="H3">
-        <v>0.1510721247563353</v>
+        <v>0.2341526520051747</v>
       </c>
       <c r="I3">
-        <v>0.138401559454191</v>
+        <v>0.2574385510996119</v>
       </c>
       <c r="J3">
-        <v>0.1017994941439917</v>
+        <v>0.1943585786371924</v>
       </c>
       <c r="K3">
-        <v>7.87</v>
+        <v>12.9</v>
       </c>
       <c r="L3">
-        <v>0.0767056530214425</v>
+        <v>0.166882276843467</v>
       </c>
       <c r="M3">
-        <v>4.13</v>
+        <v>18.13</v>
       </c>
       <c r="N3">
-        <v>0.03502968617472434</v>
+        <v>0.1106162294081757</v>
       </c>
       <c r="O3">
-        <v>0.5247776365946633</v>
+        <v>1.405426356589147</v>
       </c>
       <c r="P3">
-        <v>4.13</v>
+        <v>2.13</v>
       </c>
       <c r="Q3">
-        <v>0.03502968617472434</v>
+        <v>0.01299572910311165</v>
       </c>
       <c r="R3">
-        <v>0.5247776365946633</v>
+        <v>0.1651162790697674</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.882515168229454</v>
       </c>
       <c r="U3">
-        <v>24.9</v>
+        <v>4.89</v>
       </c>
       <c r="V3">
-        <v>0.2111959287531806</v>
+        <v>0.0298352654057352</v>
       </c>
       <c r="W3">
-        <v>0.1320469798657718</v>
+        <v>0.1274703557312253</v>
       </c>
       <c r="X3">
-        <v>0.0761687074738237</v>
+        <v>0.1028369731725362</v>
       </c>
       <c r="Y3">
-        <v>0.05587827239194812</v>
+        <v>0.0246333825586891</v>
       </c>
       <c r="Z3">
-        <v>3.755490483162517</v>
+        <v>0.7504854368932039</v>
       </c>
       <c r="AA3">
-        <v>0.3823070314485194</v>
+        <v>0.1458632828024755</v>
       </c>
       <c r="AB3">
-        <v>0.06151351716485386</v>
+        <v>0.09933090762349663</v>
       </c>
       <c r="AC3">
-        <v>0.3207935142836655</v>
+        <v>0.04653237517897883</v>
       </c>
       <c r="AD3">
-        <v>58.5</v>
+        <v>16.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>58.5</v>
+        <v>16.8</v>
       </c>
       <c r="AG3">
-        <v>33.6</v>
+        <v>11.91</v>
       </c>
       <c r="AH3">
-        <v>0.3316326530612245</v>
+        <v>0.09297177642501384</v>
       </c>
       <c r="AI3">
-        <v>0.4609929078014184</v>
+        <v>0.1781548250265111</v>
       </c>
       <c r="AJ3">
-        <v>0.2217821782178218</v>
+        <v>0.06774358682668791</v>
       </c>
       <c r="AK3">
-        <v>0.3294117647058823</v>
+        <v>0.1332065764455878</v>
       </c>
       <c r="AL3">
-        <v>1.52</v>
+        <v>2.01</v>
       </c>
       <c r="AM3">
-        <v>1.361</v>
+        <v>2.01</v>
       </c>
       <c r="AN3">
-        <v>3.774193548387097</v>
+        <v>0.835820895522388</v>
       </c>
       <c r="AO3">
-        <v>9.342105263157894</v>
+        <v>9.900497512437811</v>
       </c>
       <c r="AP3">
-        <v>2.167741935483871</v>
+        <v>0.5925373134328358</v>
       </c>
       <c r="AQ3">
-        <v>10.43350477590007</v>
+        <v>9.900497512437811</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Net Insurance S.p.A. (BIT:NET)</t>
+          <t>Assicurazioni Generali S.p.A. (BIT:G)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,46 +859,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.191</v>
+        <v>-0.005909999999999999</v>
+      </c>
+      <c r="E4">
+        <v>0.0499</v>
       </c>
       <c r="F4">
-        <v>0.382</v>
+        <v>0.0725</v>
       </c>
       <c r="G4">
-        <v>0.04269972451790634</v>
+        <v>0.08260714740829929</v>
       </c>
       <c r="H4">
-        <v>0.04269972451790634</v>
+        <v>0.08260714740829929</v>
       </c>
       <c r="I4">
-        <v>0.2479338842975207</v>
+        <v>0.0644954404104322</v>
       </c>
       <c r="J4">
-        <v>0.2140657916058986</v>
+        <v>0.04407133119375923</v>
       </c>
       <c r="K4">
-        <v>13.2</v>
+        <v>2831.9</v>
       </c>
       <c r="L4">
-        <v>0.1818181818181818</v>
+        <v>0.03372670637316726</v>
       </c>
       <c r="M4">
-        <v>0.855</v>
+        <v>2521.4</v>
       </c>
       <c r="N4">
-        <v>0.007002457002457003</v>
+        <v>0.09178573378715349</v>
       </c>
       <c r="O4">
-        <v>0.06477272727272727</v>
+        <v>0.8903562978918748</v>
       </c>
       <c r="P4">
-        <v>0.855</v>
+        <v>2521.4</v>
       </c>
       <c r="Q4">
-        <v>0.007002457002457003</v>
+        <v>0.09178573378715349</v>
       </c>
       <c r="R4">
-        <v>0.06477272727272727</v>
+        <v>0.8903562978918748</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,73 +910,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>21.5</v>
+        <v>8465.4</v>
       </c>
       <c r="V4">
-        <v>0.1760851760851761</v>
+        <v>0.3081633024517209</v>
       </c>
       <c r="W4">
-        <v>0.1629629629629629</v>
+        <v>0.08406382189239332</v>
       </c>
       <c r="X4">
-        <v>0.06587732870169054</v>
+        <v>0.1330932585924906</v>
       </c>
       <c r="Y4">
-        <v>0.09708563426127241</v>
+        <v>-0.04902943670009731</v>
       </c>
       <c r="Z4">
-        <v>0.7831715210355986</v>
+        <v>2.16139544723888</v>
       </c>
       <c r="AA4">
-        <v>0.1676502316136811</v>
+        <v>0.09525557459594805</v>
       </c>
       <c r="AB4">
-        <v>0.06044499032981372</v>
+        <v>0.09965938981218517</v>
       </c>
       <c r="AC4">
-        <v>0.1072052412838674</v>
+        <v>-0.004403815216237117</v>
       </c>
       <c r="AD4">
-        <v>23.3</v>
+        <v>21218.9</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>5.297004768038788</v>
       </c>
       <c r="AF4">
-        <v>23.3</v>
+        <v>21224.19700476804</v>
       </c>
       <c r="AG4">
-        <v>1.800000000000001</v>
+        <v>12758.79700476804</v>
       </c>
       <c r="AH4">
-        <v>0.1602475928473177</v>
+        <v>0.4358625951135877</v>
       </c>
       <c r="AI4">
-        <v>0.1871485943775101</v>
+        <v>0.4899851895924679</v>
       </c>
       <c r="AJ4">
-        <v>0.01452784503631962</v>
+        <v>0.3171518757401067</v>
       </c>
       <c r="AK4">
-        <v>0.01747572815533981</v>
+        <v>0.366099811805877</v>
       </c>
       <c r="AL4">
-        <v>3</v>
+        <v>795.5</v>
       </c>
       <c r="AM4">
-        <v>3</v>
+        <v>795.5</v>
       </c>
       <c r="AN4">
-        <v>1.273224043715847</v>
+        <v>3.46771280881322</v>
       </c>
       <c r="AO4">
-        <v>6</v>
+        <v>6.801759899434319</v>
       </c>
       <c r="AP4">
-        <v>0.09836065573770496</v>
+        <v>2.085114864506731</v>
       </c>
       <c r="AQ4">
-        <v>6</v>
+        <v>6.801759899434319</v>
       </c>
     </row>
     <row r="5">
@@ -993,121 +996,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.038</v>
-      </c>
-      <c r="E5">
-        <v>0.328</v>
+        <v>-0.0091</v>
       </c>
       <c r="G5">
-        <v>0.1165038301264206</v>
+        <v>0.09737092513358309</v>
       </c>
       <c r="H5">
-        <v>0.1165038301264206</v>
+        <v>0.09737092513358309</v>
       </c>
       <c r="I5">
-        <v>0.08077552001219077</v>
+        <v>0.08121452479022631</v>
       </c>
       <c r="J5">
-        <v>0.07155227304185674</v>
+        <v>0.06248549039134186</v>
       </c>
       <c r="K5">
-        <v>865.4</v>
+        <v>695</v>
       </c>
       <c r="L5">
-        <v>0.05072060297384261</v>
+        <v>0.0462466978526893</v>
       </c>
       <c r="M5">
-        <v>238</v>
+        <v>438.68</v>
       </c>
       <c r="N5">
-        <v>0.06136551155115511</v>
+        <v>0.1257142857142857</v>
       </c>
       <c r="O5">
-        <v>0.2750173330251907</v>
+        <v>0.6311942446043165</v>
       </c>
       <c r="P5">
-        <v>238</v>
+        <v>434.5</v>
       </c>
       <c r="Q5">
-        <v>0.06136551155115511</v>
+        <v>0.124516406361943</v>
       </c>
       <c r="R5">
-        <v>0.2750173330251907</v>
+        <v>0.625179856115108</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>4.180000000000007</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.009528585757271831</v>
       </c>
       <c r="U5">
-        <v>2627.7</v>
+        <v>1661.5</v>
       </c>
       <c r="V5">
-        <v>0.6775216584158416</v>
+        <v>0.4761427138558533</v>
       </c>
       <c r="W5">
-        <v>0.1152314882624732</v>
+        <v>0.07303181875499139</v>
       </c>
       <c r="X5">
-        <v>0.1044221867511481</v>
+        <v>0.1558562775943458</v>
       </c>
       <c r="Y5">
-        <v>0.01080930151132511</v>
+        <v>-0.08282445883935445</v>
       </c>
       <c r="Z5">
-        <v>1.78218452635867</v>
+        <v>1.483407035969519</v>
       </c>
       <c r="AA5">
-        <v>0.1275193538409877</v>
+        <v>0.09269141609252229</v>
       </c>
       <c r="AB5">
-        <v>0.06300989015841769</v>
+        <v>0.100075090228582</v>
       </c>
       <c r="AC5">
-        <v>0.06450946368257</v>
+        <v>-0.007383674136059754</v>
       </c>
       <c r="AD5">
-        <v>5175.7</v>
+        <v>4455.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5175.7</v>
+        <v>4455.3</v>
       </c>
       <c r="AG5">
-        <v>2548</v>
+        <v>2793.8</v>
       </c>
       <c r="AH5">
-        <v>0.5716415767442373</v>
+        <v>0.5607818950760246</v>
       </c>
       <c r="AI5">
-        <v>0.3048276999369814</v>
+        <v>0.3414965047829286</v>
       </c>
       <c r="AJ5">
-        <v>0.3964894808913233</v>
+        <v>0.4446389636019289</v>
       </c>
       <c r="AK5">
-        <v>0.1775436542776315</v>
+        <v>0.2453952164709396</v>
       </c>
       <c r="AL5">
-        <v>198.6</v>
+        <v>161.1</v>
       </c>
       <c r="AM5">
-        <v>198.6</v>
+        <v>161.1</v>
       </c>
       <c r="AN5">
-        <v>2.873313717870427</v>
+        <v>2.926113227374229</v>
       </c>
       <c r="AO5">
-        <v>6.939577039274925</v>
+        <v>7.576039726877716</v>
       </c>
       <c r="AP5">
-        <v>1.414533947704436</v>
+        <v>1.834887692105609</v>
       </c>
       <c r="AQ5">
-        <v>6.939577039274925</v>
+        <v>7.576039726877716</v>
       </c>
     </row>
     <row r="6">
@@ -1127,258 +1127,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.00048</v>
+        <v>0.0127</v>
       </c>
       <c r="E6">
-        <v>0.0809</v>
+        <v>0.0275</v>
       </c>
       <c r="G6">
-        <v>0.1157275161461532</v>
+        <v>0.09614412860540483</v>
       </c>
       <c r="H6">
-        <v>0.1157275161461532</v>
+        <v>0.09614412860540483</v>
       </c>
       <c r="I6">
-        <v>0.07067333782583025</v>
+        <v>0.06377717739164415</v>
       </c>
       <c r="J6">
-        <v>0.06112672530693698</v>
+        <v>0.04388376182395932</v>
       </c>
       <c r="K6">
-        <v>949.5</v>
+        <v>589.8</v>
       </c>
       <c r="L6">
-        <v>0.0566233518400353</v>
+        <v>0.03973777649016662</v>
       </c>
       <c r="M6">
-        <v>637.3</v>
+        <v>576.5999999999999</v>
       </c>
       <c r="N6">
-        <v>0.08022406847935548</v>
+        <v>0.0828591136402828</v>
       </c>
       <c r="O6">
-        <v>0.6711953659820958</v>
+        <v>0.9776195320447608</v>
       </c>
       <c r="P6">
-        <v>637.3</v>
+        <v>561.8</v>
       </c>
       <c r="Q6">
-        <v>0.08022406847935548</v>
+        <v>0.08073231016841984</v>
       </c>
       <c r="R6">
-        <v>0.6711953659820958</v>
+        <v>0.9525262800949474</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>14.79999999999995</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.02566770724939292</v>
       </c>
       <c r="U6">
-        <v>1317.1</v>
+        <v>853.6</v>
       </c>
       <c r="V6">
-        <v>0.1657980866062437</v>
+        <v>0.1226648272690694</v>
       </c>
       <c r="W6">
-        <v>0.1350755398753805</v>
+        <v>0.06235661045620341</v>
       </c>
       <c r="X6">
-        <v>0.06942906635874613</v>
+        <v>0.1111310507147736</v>
       </c>
       <c r="Y6">
-        <v>0.06564647351663441</v>
+        <v>-0.0487744402585702</v>
       </c>
       <c r="Z6">
-        <v>1.930210071942446</v>
+        <v>1.501436461852834</v>
       </c>
       <c r="AA6">
-        <v>0.117987420852309</v>
+        <v>0.06588868008575792</v>
       </c>
       <c r="AB6">
-        <v>0.06087064934076503</v>
+        <v>0.09894942263215172</v>
       </c>
       <c r="AC6">
-        <v>0.05711677151154396</v>
+        <v>-0.0330607425463938</v>
       </c>
       <c r="AD6">
-        <v>2353.1</v>
+        <v>1991.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2353.1</v>
+        <v>1991.6</v>
       </c>
       <c r="AG6">
-        <v>1036</v>
+        <v>1138</v>
       </c>
       <c r="AH6">
-        <v>0.2285206514455526</v>
+        <v>0.2225151948516267</v>
       </c>
       <c r="AI6">
-        <v>0.1942719857336283</v>
+        <v>0.2323947770685772</v>
       </c>
       <c r="AJ6">
-        <v>0.1153674832962138</v>
+        <v>0.140549352830748</v>
       </c>
       <c r="AK6">
-        <v>0.09596768964271489</v>
+        <v>0.1474800098492801</v>
       </c>
       <c r="AL6">
-        <v>108</v>
+        <v>81.2</v>
       </c>
       <c r="AM6">
-        <v>108</v>
+        <v>81.2</v>
       </c>
       <c r="AN6">
-        <v>1.425602811098994</v>
+        <v>1.563019934076283</v>
       </c>
       <c r="AO6">
-        <v>10.97314814814815</v>
+        <v>11.6576354679803</v>
       </c>
       <c r="AP6">
-        <v>0.6276505513146735</v>
+        <v>0.8931094019777115</v>
       </c>
       <c r="AQ6">
-        <v>10.97314814814815</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Assicurazioni Generali S.p.A. (BIT:G)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0347</v>
-      </c>
-      <c r="E7">
-        <v>0.0572</v>
-      </c>
-      <c r="F7">
-        <v>0.118</v>
-      </c>
-      <c r="G7">
-        <v>0.05931108994598774</v>
-      </c>
-      <c r="H7">
-        <v>0.05931108994598774</v>
-      </c>
-      <c r="I7">
-        <v>0.05511696613966548</v>
-      </c>
-      <c r="J7">
-        <v>0.03799477840652157</v>
-      </c>
-      <c r="K7">
-        <v>2976</v>
-      </c>
-      <c r="L7">
-        <v>0.02626907619532682</v>
-      </c>
-      <c r="M7">
-        <v>1862.7</v>
-      </c>
-      <c r="N7">
-        <v>0.05607569481238862</v>
-      </c>
-      <c r="O7">
-        <v>0.6259072580645162</v>
-      </c>
-      <c r="P7">
-        <v>1862.7</v>
-      </c>
-      <c r="Q7">
-        <v>0.05607569481238862</v>
-      </c>
-      <c r="R7">
-        <v>0.6259072580645162</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>8775.200000000001</v>
-      </c>
-      <c r="V7">
-        <v>0.2641732093829777</v>
-      </c>
-      <c r="W7">
-        <v>0.1011543010971979</v>
-      </c>
-      <c r="X7">
-        <v>0.08269982585188271</v>
-      </c>
-      <c r="Y7">
-        <v>0.01845447524531516</v>
-      </c>
-      <c r="Z7">
-        <v>3.12936089976496</v>
-      </c>
-      <c r="AA7">
-        <v>0.1188993739406026</v>
-      </c>
-      <c r="AB7">
-        <v>0.06199134296825828</v>
-      </c>
-      <c r="AC7">
-        <v>0.05690803097234431</v>
-      </c>
-      <c r="AD7">
-        <v>22914.4</v>
-      </c>
-      <c r="AE7">
-        <v>4.692556534121173</v>
-      </c>
-      <c r="AF7">
-        <v>22919.09255653412</v>
-      </c>
-      <c r="AG7">
-        <v>14143.89255653412</v>
-      </c>
-      <c r="AH7">
-        <v>0.4082729407945217</v>
-      </c>
-      <c r="AI7">
-        <v>0.3905443548357792</v>
-      </c>
-      <c r="AJ7">
-        <v>0.2986369684116467</v>
-      </c>
-      <c r="AK7">
-        <v>0.2833891273042853</v>
-      </c>
-      <c r="AL7">
-        <v>920.1</v>
-      </c>
-      <c r="AM7">
-        <v>920.1</v>
-      </c>
-      <c r="AN7">
-        <v>3.226294247429387</v>
-      </c>
-      <c r="AO7">
-        <v>6.782088903380067</v>
-      </c>
-      <c r="AP7">
-        <v>1.991427189514251</v>
-      </c>
-      <c r="AQ7">
-        <v>6.782088903380067</v>
+        <v>11.6576354679803</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/italy/italy_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.003395</v>
+        <v>0.00615</v>
       </c>
       <c r="E2">
-        <v>0.0387</v>
+        <v>0.0331</v>
       </c>
       <c r="F2">
-        <v>0.15575</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="G2">
-        <v>0.08642148712447482</v>
+        <v>0.08527131782945736</v>
       </c>
       <c r="H2">
-        <v>0.08642148712447482</v>
+        <v>0.08527131782945736</v>
       </c>
       <c r="I2">
-        <v>0.06673845134695175</v>
+        <v>0.09489851861319148</v>
       </c>
       <c r="J2">
-        <v>0.0483146850900994</v>
+        <v>0.06975030077303929</v>
       </c>
       <c r="K2">
-        <v>4129.6</v>
+        <v>6465.9</v>
       </c>
       <c r="L2">
-        <v>0.03625197298308019</v>
+        <v>0.05484544897029597</v>
       </c>
       <c r="M2">
-        <v>3554.81</v>
+        <v>3469.2334</v>
       </c>
       <c r="N2">
-        <v>0.09334448450346221</v>
+        <v>0.08062978104293381</v>
       </c>
       <c r="O2">
-        <v>0.860812185199535</v>
+        <v>0.5365430025209175</v>
       </c>
       <c r="P2">
-        <v>3519.83</v>
+        <v>2714.8334</v>
       </c>
       <c r="Q2">
-        <v>0.0924259571931612</v>
+        <v>0.06309648195190429</v>
       </c>
       <c r="R2">
-        <v>0.8523416311507167</v>
+        <v>0.4198693762662584</v>
       </c>
       <c r="S2">
-        <v>34.97999999999996</v>
+        <v>754.4000000000001</v>
       </c>
       <c r="T2">
-        <v>0.00984018836449767</v>
+        <v>0.2174543805556582</v>
       </c>
       <c r="U2">
-        <v>10985.39</v>
+        <v>8525.1</v>
       </c>
       <c r="V2">
-        <v>0.2884614273672823</v>
+        <v>0.1981351114540506</v>
       </c>
       <c r="W2">
-        <v>0.07854782032369236</v>
+        <v>0.1792876110246314</v>
       </c>
       <c r="X2">
-        <v>0.1221121546536321</v>
+        <v>0.1316654971622319</v>
       </c>
       <c r="Y2">
-        <v>-0.04356433432993977</v>
+        <v>0.04762211386239959</v>
       </c>
       <c r="Z2">
-        <v>1.931813153836593</v>
+        <v>3.049091123870594</v>
       </c>
       <c r="AA2">
-        <v>0.09397349534423517</v>
+        <v>0.1493611462255704</v>
       </c>
       <c r="AB2">
-        <v>0.0994951487178409</v>
+        <v>0.08850802572851343</v>
       </c>
       <c r="AC2">
-        <v>-0.005893744676148435</v>
+        <v>0.06083484703807085</v>
       </c>
       <c r="AD2">
-        <v>27682.6</v>
+        <v>45893.5</v>
       </c>
       <c r="AE2">
-        <v>5.297004768038788</v>
+        <v>6.997276415763948</v>
       </c>
       <c r="AF2">
-        <v>27687.89700476804</v>
+        <v>45900.49727641576</v>
       </c>
       <c r="AG2">
-        <v>16702.50700476804</v>
+        <v>37375.39727641577</v>
       </c>
       <c r="AH2">
-        <v>0.4209768234696245</v>
+        <v>0.5161581460139975</v>
       </c>
       <c r="AI2">
-        <v>0.4257934180799565</v>
+        <v>0.4852999956457875</v>
       </c>
       <c r="AJ2">
-        <v>0.3048725726876307</v>
+        <v>0.4648559993145731</v>
       </c>
       <c r="AK2">
-        <v>0.3090698363434848</v>
+        <v>0.434311818725125</v>
       </c>
       <c r="AL2">
-        <v>1039.81</v>
+        <v>1086</v>
       </c>
       <c r="AM2">
-        <v>1039.81</v>
+        <v>851.1</v>
       </c>
       <c r="AN2">
-        <v>3.097911903570882</v>
+        <v>3.721895305044004</v>
       </c>
       <c r="AO2">
-        <v>7.306911839663016</v>
+        <v>10.2963167587477</v>
       </c>
       <c r="AP2">
-        <v>1.869148680743389</v>
+        <v>3.031089710901245</v>
       </c>
       <c r="AQ2">
-        <v>7.306911839663016</v>
+        <v>13.13805663259311</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Net Insurance S.p.A. (BIT:NET)</t>
+          <t>Assicurazioni Generali S.p.A. (BIT:G)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.181</v>
+        <v>0.00615</v>
+      </c>
+      <c r="E3">
+        <v>0.141</v>
       </c>
       <c r="F3">
-        <v>0.239</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2341526520051747</v>
+        <v>0.07933957369610356</v>
       </c>
       <c r="H3">
-        <v>0.2341526520051747</v>
+        <v>0.07933957369610356</v>
       </c>
       <c r="I3">
-        <v>0.2574385510996119</v>
+        <v>0.0992332272943165</v>
       </c>
       <c r="J3">
-        <v>0.1943585786371924</v>
+        <v>0.07068274971376937</v>
       </c>
       <c r="K3">
-        <v>12.9</v>
+        <v>4684.5</v>
       </c>
       <c r="L3">
-        <v>0.166882276843467</v>
+        <v>0.05365162008537073</v>
       </c>
       <c r="M3">
-        <v>18.13</v>
+        <v>2700.9</v>
       </c>
       <c r="N3">
-        <v>0.1106162294081757</v>
+        <v>0.08475060247012753</v>
       </c>
       <c r="O3">
-        <v>1.405426356589147</v>
+        <v>0.5765609990393852</v>
       </c>
       <c r="P3">
-        <v>2.13</v>
+        <v>1946.5</v>
       </c>
       <c r="Q3">
-        <v>0.01299572910311165</v>
+        <v>0.06107854704287579</v>
       </c>
       <c r="R3">
-        <v>0.1651162790697674</v>
+        <v>0.4155192656633579</v>
       </c>
       <c r="S3">
-        <v>16</v>
+        <v>754.4000000000001</v>
       </c>
       <c r="T3">
-        <v>0.882515168229454</v>
+        <v>0.2793143026398608</v>
       </c>
       <c r="U3">
-        <v>4.89</v>
+        <v>6938.9</v>
       </c>
       <c r="V3">
-        <v>0.0298352654057352</v>
+        <v>0.2177333316598052</v>
       </c>
       <c r="W3">
-        <v>0.1274703557312253</v>
+        <v>0.23488738241842</v>
       </c>
       <c r="X3">
-        <v>0.1028369731725362</v>
+        <v>0.1316654971622319</v>
       </c>
       <c r="Y3">
-        <v>0.0246333825586891</v>
+        <v>0.1032218852561881</v>
       </c>
       <c r="Z3">
-        <v>0.7504854368932039</v>
+        <v>3.55652131903143</v>
       </c>
       <c r="AA3">
-        <v>0.1458632828024755</v>
+        <v>0.2513847062447835</v>
       </c>
       <c r="AB3">
-        <v>0.09933090762349663</v>
+        <v>0.08850802572851343</v>
       </c>
       <c r="AC3">
-        <v>0.04653237517897883</v>
+        <v>0.1628766805162701</v>
       </c>
       <c r="AD3">
-        <v>16.8</v>
+        <v>38115.7</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>6.997276415763948</v>
       </c>
       <c r="AF3">
-        <v>16.8</v>
+        <v>38122.69727641576</v>
       </c>
       <c r="AG3">
-        <v>11.91</v>
+        <v>31183.79727641576</v>
       </c>
       <c r="AH3">
-        <v>0.09297177642501384</v>
+        <v>0.5446761215274293</v>
       </c>
       <c r="AI3">
-        <v>0.1781548250265111</v>
+        <v>0.5466787710255158</v>
       </c>
       <c r="AJ3">
-        <v>0.06774358682668791</v>
+        <v>0.49456800549721</v>
       </c>
       <c r="AK3">
-        <v>0.1332065764455878</v>
+        <v>0.4965873512873907</v>
       </c>
       <c r="AL3">
-        <v>2.01</v>
+        <v>900.7</v>
       </c>
       <c r="AM3">
-        <v>2.01</v>
+        <v>900.7</v>
       </c>
       <c r="AN3">
-        <v>0.835820895522388</v>
+        <v>4.127496865044214</v>
       </c>
       <c r="AO3">
-        <v>9.900497512437811</v>
+        <v>9.612856667036748</v>
       </c>
       <c r="AP3">
-        <v>0.5925373134328358</v>
+        <v>3.376850628443931</v>
       </c>
       <c r="AQ3">
-        <v>9.900497512437811</v>
+        <v>9.612856667036748</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Assicurazioni Generali S.p.A. (BIT:G)</t>
+          <t>Unipol Gruppo S.p.A. (BIT:UNI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,49 +862,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.005909999999999999</v>
+        <v>0.0177</v>
       </c>
       <c r="E4">
-        <v>0.0499</v>
-      </c>
-      <c r="F4">
-        <v>0.0725</v>
+        <v>0.0331</v>
       </c>
       <c r="G4">
-        <v>0.08260714740829929</v>
+        <v>0.09984323836846851</v>
       </c>
       <c r="H4">
-        <v>0.08260714740829929</v>
+        <v>0.09984323836846851</v>
       </c>
       <c r="I4">
-        <v>0.0644954404104322</v>
+        <v>0.0965990594302108</v>
       </c>
       <c r="J4">
-        <v>0.04407133119375923</v>
+        <v>0.07165979299601445</v>
       </c>
       <c r="K4">
-        <v>2831.9</v>
+        <v>802.4</v>
       </c>
       <c r="L4">
-        <v>0.03372670637316726</v>
+        <v>0.04856584291152954</v>
       </c>
       <c r="M4">
-        <v>2521.4</v>
+        <v>290.3</v>
       </c>
       <c r="N4">
-        <v>0.09178573378715349</v>
+        <v>0.07094677159196441</v>
       </c>
       <c r="O4">
-        <v>0.8903562978918748</v>
+        <v>0.36178963110668</v>
       </c>
       <c r="P4">
-        <v>2521.4</v>
+        <v>290.3</v>
       </c>
       <c r="Q4">
-        <v>0.09178573378715349</v>
+        <v>0.07094677159196441</v>
       </c>
       <c r="R4">
-        <v>0.8903562978918748</v>
+        <v>0.36178963110668</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -910,73 +910,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8465.4</v>
+        <v>1586.2</v>
       </c>
       <c r="V4">
-        <v>0.3081633024517209</v>
+        <v>0.3876533554914707</v>
       </c>
       <c r="W4">
-        <v>0.08406382189239332</v>
+        <v>0.1163944413821115</v>
       </c>
       <c r="X4">
-        <v>0.1330932585924906</v>
+        <v>0.1333661036191338</v>
       </c>
       <c r="Y4">
-        <v>-0.04902943670009731</v>
+        <v>-0.01697166223702233</v>
       </c>
       <c r="Z4">
-        <v>2.16139544723888</v>
+        <v>2.084308926679114</v>
       </c>
       <c r="AA4">
-        <v>0.09525557459594805</v>
+        <v>0.1493611462255704</v>
       </c>
       <c r="AB4">
-        <v>0.09965938981218517</v>
+        <v>0.08852629918749952</v>
       </c>
       <c r="AC4">
-        <v>-0.004403815216237117</v>
+        <v>0.06083484703807085</v>
       </c>
       <c r="AD4">
-        <v>21218.9</v>
+        <v>5083</v>
       </c>
       <c r="AE4">
-        <v>5.297004768038788</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>21224.19700476804</v>
+        <v>5083</v>
       </c>
       <c r="AG4">
-        <v>12758.79700476804</v>
+        <v>3496.8</v>
       </c>
       <c r="AH4">
-        <v>0.4358625951135877</v>
+        <v>0.5540175262676026</v>
       </c>
       <c r="AI4">
-        <v>0.4899851895924679</v>
+        <v>0.3428829691789832</v>
       </c>
       <c r="AJ4">
-        <v>0.3171518757401067</v>
+        <v>0.4607964578446617</v>
       </c>
       <c r="AK4">
-        <v>0.366099811805877</v>
+        <v>0.2641466675731412</v>
       </c>
       <c r="AL4">
-        <v>795.5</v>
+        <v>185.3</v>
       </c>
       <c r="AM4">
-        <v>795.5</v>
+        <v>185.3</v>
       </c>
       <c r="AN4">
-        <v>3.46771280881322</v>
+        <v>2.600399038215583</v>
       </c>
       <c r="AO4">
-        <v>6.801759899434319</v>
+        <v>8.613059902860225</v>
       </c>
       <c r="AP4">
-        <v>2.085114864506731</v>
+        <v>1.788919015705735</v>
       </c>
       <c r="AQ4">
-        <v>6.801759899434319</v>
+        <v>8.613059902860225</v>
       </c>
     </row>
     <row r="5">
@@ -987,7 +987,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unipol Gruppo S.p.A. (BIT:UNI)</t>
+          <t>UnipolSai Assicurazioni S.p.A. (BIT:US)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -996,252 +996,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0091</v>
+        <v>-0.00073</v>
+      </c>
+      <c r="E5">
+        <v>0.00976</v>
       </c>
       <c r="G5">
-        <v>0.09737092513358309</v>
+        <v>0.1049872313787977</v>
       </c>
       <c r="H5">
-        <v>0.09737092513358309</v>
+        <v>0.1049872313787977</v>
       </c>
       <c r="I5">
-        <v>0.08121452479022631</v>
+        <v>0.06597713741028176</v>
       </c>
       <c r="J5">
-        <v>0.06248549039134186</v>
+        <v>0.04954093587516624</v>
       </c>
       <c r="K5">
-        <v>695</v>
+        <v>979</v>
       </c>
       <c r="L5">
-        <v>0.0462466978526893</v>
+        <v>0.06964055797807639</v>
       </c>
       <c r="M5">
-        <v>438.68</v>
+        <v>478.0334</v>
       </c>
       <c r="N5">
-        <v>0.1257142857142857</v>
+        <v>0.06765166074638061</v>
       </c>
       <c r="O5">
-        <v>0.6311942446043165</v>
+        <v>0.4882874361593463</v>
       </c>
       <c r="P5">
-        <v>434.5</v>
+        <v>478.0334</v>
       </c>
       <c r="Q5">
-        <v>0.124516406361943</v>
+        <v>0.06765166074638061</v>
       </c>
       <c r="R5">
-        <v>0.625179856115108</v>
+        <v>0.4882874361593463</v>
       </c>
       <c r="S5">
-        <v>4.180000000000007</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.009528585757271831</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1661.5</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.4761427138558533</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.07303181875499139</v>
+        <v>0.1792876110246314</v>
       </c>
       <c r="X5">
-        <v>0.1558562775943458</v>
+        <v>0.1015411620155286</v>
       </c>
       <c r="Y5">
-        <v>-0.08282445883935445</v>
+        <v>0.07774644900910284</v>
       </c>
       <c r="Z5">
-        <v>1.483407035969519</v>
+        <v>2.271800258564964</v>
       </c>
       <c r="AA5">
-        <v>0.09269141609252229</v>
+        <v>0.112547110930753</v>
       </c>
       <c r="AB5">
-        <v>0.100075090228582</v>
+        <v>0.08798260580901565</v>
       </c>
       <c r="AC5">
-        <v>-0.007383674136059754</v>
+        <v>0.02456450512173734</v>
       </c>
       <c r="AD5">
-        <v>4455.3</v>
+        <v>2694.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>4455.3</v>
+        <v>2694.8</v>
       </c>
       <c r="AG5">
-        <v>2793.8</v>
+        <v>2694.8</v>
       </c>
       <c r="AH5">
-        <v>0.5607818950760246</v>
+        <v>0.2760810990789784</v>
       </c>
       <c r="AI5">
-        <v>0.3414965047829286</v>
+        <v>0.2688803967153249</v>
       </c>
       <c r="AJ5">
-        <v>0.4446389636019289</v>
+        <v>0.2760810990789784</v>
       </c>
       <c r="AK5">
-        <v>0.2453952164709396</v>
+        <v>0.2688803967153249</v>
       </c>
       <c r="AL5">
-        <v>161.1</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>161.1</v>
+        <v>-234.9</v>
       </c>
       <c r="AN5">
-        <v>2.926113227374229</v>
-      </c>
-      <c r="AO5">
-        <v>7.576039726877716</v>
+        <v>2.360960224285964</v>
       </c>
       <c r="AP5">
-        <v>1.834887692105609</v>
+        <v>2.360960224285964</v>
       </c>
       <c r="AQ5">
-        <v>7.576039726877716</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>UnipolSai Assicurazioni S.p.A. (BIT:US)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0127</v>
-      </c>
-      <c r="E6">
-        <v>0.0275</v>
-      </c>
-      <c r="G6">
-        <v>0.09614412860540483</v>
-      </c>
-      <c r="H6">
-        <v>0.09614412860540483</v>
-      </c>
-      <c r="I6">
-        <v>0.06377717739164415</v>
-      </c>
-      <c r="J6">
-        <v>0.04388376182395932</v>
-      </c>
-      <c r="K6">
-        <v>589.8</v>
-      </c>
-      <c r="L6">
-        <v>0.03973777649016662</v>
-      </c>
-      <c r="M6">
-        <v>576.5999999999999</v>
-      </c>
-      <c r="N6">
-        <v>0.0828591136402828</v>
-      </c>
-      <c r="O6">
-        <v>0.9776195320447608</v>
-      </c>
-      <c r="P6">
-        <v>561.8</v>
-      </c>
-      <c r="Q6">
-        <v>0.08073231016841984</v>
-      </c>
-      <c r="R6">
-        <v>0.9525262800949474</v>
-      </c>
-      <c r="S6">
-        <v>14.79999999999995</v>
-      </c>
-      <c r="T6">
-        <v>0.02566770724939292</v>
-      </c>
-      <c r="U6">
-        <v>853.6</v>
-      </c>
-      <c r="V6">
-        <v>0.1226648272690694</v>
-      </c>
-      <c r="W6">
-        <v>0.06235661045620341</v>
-      </c>
-      <c r="X6">
-        <v>0.1111310507147736</v>
-      </c>
-      <c r="Y6">
-        <v>-0.0487744402585702</v>
-      </c>
-      <c r="Z6">
-        <v>1.501436461852834</v>
-      </c>
-      <c r="AA6">
-        <v>0.06588868008575792</v>
-      </c>
-      <c r="AB6">
-        <v>0.09894942263215172</v>
-      </c>
-      <c r="AC6">
-        <v>-0.0330607425463938</v>
-      </c>
-      <c r="AD6">
-        <v>1991.6</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>1991.6</v>
-      </c>
-      <c r="AG6">
-        <v>1138</v>
-      </c>
-      <c r="AH6">
-        <v>0.2225151948516267</v>
-      </c>
-      <c r="AI6">
-        <v>0.2323947770685772</v>
-      </c>
-      <c r="AJ6">
-        <v>0.140549352830748</v>
-      </c>
-      <c r="AK6">
-        <v>0.1474800098492801</v>
-      </c>
-      <c r="AL6">
-        <v>81.2</v>
-      </c>
-      <c r="AM6">
-        <v>81.2</v>
-      </c>
-      <c r="AN6">
-        <v>1.563019934076283</v>
-      </c>
-      <c r="AO6">
-        <v>11.6576354679803</v>
-      </c>
-      <c r="AP6">
-        <v>0.8931094019777115</v>
-      </c>
-      <c r="AQ6">
-        <v>11.6576354679803</v>
+        <v>-3.948488718603661</v>
       </c>
     </row>
   </sheetData>
